--- a/public/posts/harry-browne-permanent-portfolio/Stocks_Bonds_Gold_Cash_Summary_Stats.xlsx
+++ b/public/posts/harry-browne-permanent-portfolio/Stocks_Bonds_Gold_Cash_Summary_Stats.xlsx
@@ -435,7 +435,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Annualized Mean</t>
+          <t>Annual Mean Return (Arithmetic)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -450,7 +450,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>CAGR</t>
+          <t>CAGR (Geometric)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Days to Recover</t>
+          <t>Calendar Days to Recovery</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
